--- a/base_prov/ml/ml_abbott_2026-09-11.xlsx
+++ b/base_prov/ml/ml_abbott_2026-09-11.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\como se me cante\retail-chatbot-main\eci_abbott-main\base_prov\ml\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C097A3ED-6C46-44CA-9719-C1C2EECAA373}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA5BA2E2-8745-440A-96D1-291DEA56D2C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="701" uniqueCount="173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="701" uniqueCount="172">
   <si>
     <t>fecha</t>
   </si>
@@ -407,9 +407,6 @@
     <t>GRUPOBEBE</t>
   </si>
   <si>
-    <t>https://www.mercadolibre.com.mx/similac-isomil-1-formula-no-lactea-para-lactantes-para-lactantes-con-necesidades-especiales-de-nutricion-de-0-a-12-meses-850g/p/MLM15186216#polycard_client=search-desktop&amp;be_origin=backend&amp;overlay_label=not_apply&amp;search_layout=grid&amp;position=3&amp;type=product&amp;tracking_id=3a55c658-7ffa-4e5e-a990-b6341dce8fa5&amp;wid=MLM5158444360&amp;sid=search</t>
-  </si>
-  <si>
     <t>https://www.mercadolibre.com.mx/similac-arroz-advance-formula-con-hierro-no-lactea-para-lactantes-con-necesidades-especiales-de-nutricion-0-a-12-meses-400g/p/MLM22271980#polycard_client=search-desktop&amp;be_origin=backend&amp;overlay_label=not_apply&amp;search_layout=grid&amp;position=2&amp;type=product&amp;tracking_id=41fff0b2-0b86-4ae6-9189-992db285c874&amp;wid=MLM1891284787&amp;sid=search</t>
   </si>
   <si>
@@ -470,9 +467,6 @@
     <t>https://www.mercadolibre.com.mx/similac-etapa-3-formula-de-continuacion-para-lactantes-de-1-a-3-anos-1800g/p/MLM34562469?pdp_filters=item_id:MLM2990111850#is_advertising=true&amp;searchVariation=MLM34562469&amp;backend_model=search-backend;EQ:SIMILAC%20ETAPA%203%20FORMULA%20CONTINUACION%201800G;EQ:SIMILAC%201800G;EQ:SIMILAC%20ETAPA%203%20LACTANTE%201A3%20ANOS;EQ:SIMILAC%201%20ANO&amp;be_origin=backend&amp;position=1&amp;search_layout=grid&amp;type=pad&amp;tracking_id=4c05d5e2-b679-4540-b44e-fcca560ef875&amp;ad_domain=VQCATCORE_LST&amp;ad_position=1&amp;ad_click_id=ZGU4NDZjOTEtNjMyMi00YjBhLThlNmYtZDg0NjFlNmMyMDg5</t>
   </si>
   <si>
-    <t>SYMGROUP</t>
-  </si>
-  <si>
     <t>https://www.mercadolibre.com.mx/similac-ar-formula-con-hierro-a-base-de-almidon-de-arroz-para-lactantes-con-necesidades-especiales-de-nutricion-0-a-12-meses-350g/p/MLM36975271#polycard_client=search-desktop&amp;be_origin=backend&amp;overlay_label=not_apply&amp;search_layout=grid&amp;position=2&amp;type=product&amp;tracking_id=953e609c-24c7-4734-ba52-6aba3fe834c6&amp;wid=MLM3297863657&amp;sid=search</t>
   </si>
   <si>
@@ -555,6 +549,9 @@
   </si>
   <si>
     <t>2026-09-11</t>
+  </si>
+  <si>
+    <t>https://www.mercadolibre.com.mx/similac-isomil-1-formula-no-lactea-para-lactantes-para-lactantes-con-necesidades-especiales-de-nutricion-de-0-a-12-meses-850g/p/MLM15186216?pdp_filters=item_id:MLM1378980533#intervention_type=MARKET&amp;position=3&amp;search_layout=grid&amp;type=cart_intervention&amp;tracking_id=6ca14262-8e5f-4703-a8d7-eb6bcad9a81c</t>
   </si>
 </sst>
 </file>
@@ -999,7 +996,7 @@
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B2" t="s">
         <v>13</v>
@@ -1046,7 +1043,7 @@
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B3" t="s">
         <v>13</v>
@@ -1093,7 +1090,7 @@
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B4" t="s">
         <v>13</v>
@@ -1140,7 +1137,7 @@
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B5" t="s">
         <v>13</v>
@@ -1187,7 +1184,7 @@
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B6" t="s">
         <v>13</v>
@@ -1234,7 +1231,7 @@
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B7" t="s">
         <v>13</v>
@@ -1281,7 +1278,7 @@
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B8" t="s">
         <v>13</v>
@@ -1328,7 +1325,7 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B9" t="s">
         <v>13</v>
@@ -1375,7 +1372,7 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B10" t="s">
         <v>13</v>
@@ -1422,7 +1419,7 @@
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B11" t="s">
         <v>13</v>
@@ -1469,7 +1466,7 @@
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B12" t="s">
         <v>13</v>
@@ -1516,7 +1513,7 @@
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B13" t="s">
         <v>13</v>
@@ -1563,7 +1560,7 @@
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B14" t="s">
         <v>13</v>
@@ -1610,7 +1607,7 @@
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B15" t="s">
         <v>13</v>
@@ -1657,13 +1654,13 @@
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B16" t="s">
         <v>13</v>
       </c>
       <c r="C16" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D16">
         <v>3537789844</v>
@@ -1696,7 +1693,7 @@
         <v>1912</v>
       </c>
       <c r="N16" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="O16" t="s">
         <v>9</v>
@@ -1704,7 +1701,7 @@
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B17" t="s">
         <v>13</v>
@@ -1751,7 +1748,7 @@
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B18" t="s">
         <v>13</v>
@@ -1798,7 +1795,7 @@
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B19" t="s">
         <v>13</v>
@@ -1845,13 +1842,13 @@
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B20" t="s">
         <v>13</v>
       </c>
       <c r="C20" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="D20">
         <v>3880978850</v>
@@ -1884,7 +1881,7 @@
         <v>1008</v>
       </c>
       <c r="N20" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="O20" t="s">
         <v>9</v>
@@ -1892,7 +1889,7 @@
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B21" t="s">
         <v>13</v>
@@ -1939,7 +1936,7 @@
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B22" t="s">
         <v>13</v>
@@ -1986,7 +1983,7 @@
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B23" t="s">
         <v>13</v>
@@ -2033,7 +2030,7 @@
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B24" t="s">
         <v>13</v>
@@ -2080,7 +2077,7 @@
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B25" t="s">
         <v>13</v>
@@ -2127,7 +2124,7 @@
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B26" t="s">
         <v>13</v>
@@ -2174,7 +2171,7 @@
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B27" t="s">
         <v>13</v>
@@ -2221,7 +2218,7 @@
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B28" t="s">
         <v>13</v>
@@ -2236,7 +2233,7 @@
         <v>31</v>
       </c>
       <c r="F28" t="s">
-        <v>122</v>
+        <v>7</v>
       </c>
       <c r="G28">
         <v>1000</v>
@@ -2260,21 +2257,21 @@
         <v>425</v>
       </c>
       <c r="N28" t="s">
-        <v>123</v>
+        <v>171</v>
       </c>
       <c r="O28" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B29" t="s">
         <v>13</v>
       </c>
       <c r="C29" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D29">
         <v>2334097590</v>
@@ -2307,7 +2304,7 @@
         <v>606</v>
       </c>
       <c r="N29" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="O29" t="s">
         <v>9</v>
@@ -2315,7 +2312,7 @@
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B30" t="s">
         <v>13</v>
@@ -2354,7 +2351,7 @@
         <v>850</v>
       </c>
       <c r="N30" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="O30" t="s">
         <v>9</v>
@@ -2362,7 +2359,7 @@
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B31" t="s">
         <v>13</v>
@@ -2401,7 +2398,7 @@
         <v>1356</v>
       </c>
       <c r="N31" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="O31" t="s">
         <v>9</v>
@@ -2409,13 +2406,13 @@
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B32" t="s">
         <v>13</v>
       </c>
       <c r="C32" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D32">
         <v>2042277005</v>
@@ -2448,7 +2445,7 @@
         <v>463</v>
       </c>
       <c r="N32" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="O32" t="s">
         <v>9</v>
@@ -2456,7 +2453,7 @@
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B33" t="s">
         <v>13</v>
@@ -2495,7 +2492,7 @@
         <v>1095</v>
       </c>
       <c r="N33" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="O33" t="s">
         <v>9</v>
@@ -2503,7 +2500,7 @@
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B34" t="s">
         <v>13</v>
@@ -2542,7 +2539,7 @@
         <v>1130</v>
       </c>
       <c r="N34" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="O34" t="s">
         <v>9</v>
@@ -2550,7 +2547,7 @@
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B35" t="s">
         <v>13</v>
@@ -2565,7 +2562,7 @@
         <v>30</v>
       </c>
       <c r="F35" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="G35">
         <v>5000</v>
@@ -2589,7 +2586,7 @@
         <v>1094</v>
       </c>
       <c r="N35" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="O35" t="s">
         <v>11</v>
@@ -2597,7 +2594,7 @@
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B36" t="s">
         <v>13</v>
@@ -2636,7 +2633,7 @@
         <v>1562</v>
       </c>
       <c r="N36" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="O36" t="s">
         <v>9</v>
@@ -2644,7 +2641,7 @@
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B37" t="s">
         <v>13</v>
@@ -2683,7 +2680,7 @@
         <v>1524</v>
       </c>
       <c r="N37" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="O37" t="s">
         <v>9</v>
@@ -2691,7 +2688,7 @@
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B38" t="s">
         <v>13</v>
@@ -2738,7 +2735,7 @@
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B39" t="s">
         <v>13</v>
@@ -2785,7 +2782,7 @@
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B40" t="s">
         <v>13</v>
@@ -2832,13 +2829,13 @@
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B41" t="s">
         <v>13</v>
       </c>
       <c r="C41" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="D41">
         <v>2035806901</v>
@@ -2871,7 +2868,7 @@
         <v>749</v>
       </c>
       <c r="N41" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="O41" t="s">
         <v>9</v>
@@ -2879,7 +2876,7 @@
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B42" t="s">
         <v>13</v>
@@ -2926,7 +2923,7 @@
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B43" t="s">
         <v>13</v>
@@ -2973,7 +2970,7 @@
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B44" t="s">
         <v>13</v>
@@ -3020,7 +3017,7 @@
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B45" t="s">
         <v>13</v>
@@ -3067,7 +3064,7 @@
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B46" t="s">
         <v>13</v>
@@ -3106,7 +3103,7 @@
         <v>1974</v>
       </c>
       <c r="N46" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="O46" t="s">
         <v>9</v>
@@ -3114,7 +3111,7 @@
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B47" t="s">
         <v>13</v>
@@ -3161,7 +3158,7 @@
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B48" t="s">
         <v>13</v>
@@ -3200,7 +3197,7 @@
         <v>681</v>
       </c>
       <c r="N48" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="O48" t="s">
         <v>9</v>
@@ -3208,7 +3205,7 @@
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B49" t="s">
         <v>13</v>
@@ -3247,7 +3244,7 @@
         <v>1343</v>
       </c>
       <c r="N49" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="O49" t="s">
         <v>9</v>
@@ -3255,13 +3252,13 @@
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B50" t="s">
         <v>13</v>
       </c>
       <c r="C50" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="D50">
         <v>1386166955</v>
@@ -3294,7 +3291,7 @@
         <v>450</v>
       </c>
       <c r="N50" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="O50" t="s">
         <v>9</v>
@@ -3302,7 +3299,7 @@
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B51" t="s">
         <v>13</v>
@@ -3341,7 +3338,7 @@
         <v>1309</v>
       </c>
       <c r="N51" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="O51" t="s">
         <v>9</v>
@@ -3349,7 +3346,7 @@
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B52" t="s">
         <v>13</v>
@@ -3388,7 +3385,7 @@
         <v>1305</v>
       </c>
       <c r="N52" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="O52" t="s">
         <v>9</v>
@@ -3396,13 +3393,13 @@
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B53" t="s">
         <v>13</v>
       </c>
       <c r="C53" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D53">
         <v>1344836181</v>
@@ -3435,7 +3432,7 @@
         <v>1324</v>
       </c>
       <c r="N53" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="O53" t="s">
         <v>9</v>
@@ -3443,7 +3440,7 @@
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B54" t="s">
         <v>13</v>
@@ -3482,7 +3479,7 @@
         <v>1202</v>
       </c>
       <c r="N54" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="O54" t="s">
         <v>9</v>
@@ -3490,7 +3487,7 @@
     </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B55" t="s">
         <v>13</v>
@@ -3529,7 +3526,7 @@
         <v>1923</v>
       </c>
       <c r="N55" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="O55" t="s">
         <v>9</v>
@@ -3537,7 +3534,7 @@
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B56" t="s">
         <v>13</v>
@@ -3576,7 +3573,7 @@
         <v>1078</v>
       </c>
       <c r="N56" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="O56" t="s">
         <v>9</v>
@@ -3584,7 +3581,7 @@
     </row>
     <row r="57" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B57" t="s">
         <v>13</v>
@@ -3623,7 +3620,7 @@
         <v>1948</v>
       </c>
       <c r="N57" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="O57" t="s">
         <v>9</v>
@@ -3631,13 +3628,13 @@
     </row>
     <row r="58" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B58" t="s">
         <v>13</v>
       </c>
       <c r="C58" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="D58">
         <v>2035712373</v>
@@ -3670,7 +3667,7 @@
         <v>620</v>
       </c>
       <c r="N58" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="O58" t="s">
         <v>9</v>
@@ -3678,7 +3675,7 @@
     </row>
     <row r="59" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B59" t="s">
         <v>13</v>
@@ -3725,7 +3722,7 @@
     </row>
     <row r="60" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B60" t="s">
         <v>13</v>
@@ -3764,7 +3761,7 @@
         <v>1905</v>
       </c>
       <c r="N60" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="O60" t="s">
         <v>9</v>
@@ -3772,7 +3769,7 @@
     </row>
     <row r="61" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B61" t="s">
         <v>13</v>
@@ -3811,7 +3808,7 @@
         <v>1550</v>
       </c>
       <c r="N61" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="O61" t="s">
         <v>9</v>
@@ -3819,7 +3816,7 @@
     </row>
     <row r="62" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B62" t="s">
         <v>13</v>
@@ -3858,7 +3855,7 @@
         <v>488</v>
       </c>
       <c r="N62" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="O62" t="s">
         <v>9</v>
@@ -3866,7 +3863,7 @@
     </row>
     <row r="63" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B63" t="s">
         <v>13</v>
@@ -3913,7 +3910,7 @@
     </row>
     <row r="64" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B64" t="s">
         <v>13</v>
@@ -3952,7 +3949,7 @@
         <v>527</v>
       </c>
       <c r="N64" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="O64" t="s">
         <v>9</v>
@@ -3960,7 +3957,7 @@
     </row>
     <row r="65" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B65" t="s">
         <v>13</v>
@@ -3999,7 +3996,7 @@
         <v>418</v>
       </c>
       <c r="N65" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="O65" t="s">
         <v>9</v>
@@ -4007,7 +4004,7 @@
     </row>
     <row r="66" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B66" t="s">
         <v>13</v>
@@ -4022,7 +4019,7 @@
         <v>31</v>
       </c>
       <c r="F66" t="s">
-        <v>144</v>
+        <v>122</v>
       </c>
       <c r="G66">
         <v>100</v>
@@ -4046,7 +4043,7 @@
         <v>711</v>
       </c>
       <c r="N66" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="O66" t="s">
         <v>11</v>
@@ -4054,7 +4051,7 @@
     </row>
     <row r="67" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B67" t="s">
         <v>13</v>
@@ -4069,10 +4066,10 @@
         <v>31</v>
       </c>
       <c r="F67" t="s">
-        <v>144</v>
+        <v>7</v>
       </c>
       <c r="G67">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -4093,21 +4090,21 @@
         <v>711</v>
       </c>
       <c r="N67" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="O67" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="68" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B68" t="s">
         <v>13</v>
       </c>
       <c r="C68" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="D68">
         <v>2261286679</v>
@@ -4140,7 +4137,7 @@
         <v>658</v>
       </c>
       <c r="N68" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="O68" t="s">
         <v>9</v>
@@ -4148,7 +4145,7 @@
     </row>
     <row r="69" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B69" t="s">
         <v>13</v>
@@ -4187,7 +4184,7 @@
         <v>661</v>
       </c>
       <c r="N69" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="O69" t="s">
         <v>9</v>
@@ -4195,7 +4192,7 @@
     </row>
     <row r="70" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B70" t="s">
         <v>13</v>
@@ -4242,7 +4239,7 @@
     </row>
     <row r="71" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B71" t="s">
         <v>13</v>
@@ -4289,7 +4286,7 @@
     </row>
     <row r="72" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B72" t="s">
         <v>13</v>
@@ -4328,7 +4325,7 @@
         <v>674</v>
       </c>
       <c r="N72" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="O72" t="s">
         <v>9</v>
@@ -4336,7 +4333,7 @@
     </row>
     <row r="73" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B73" t="s">
         <v>13</v>
@@ -4351,7 +4348,7 @@
         <v>29</v>
       </c>
       <c r="F73" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="G73">
         <v>5000</v>
@@ -4375,7 +4372,7 @@
         <v>660</v>
       </c>
       <c r="N73" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="O73" t="s">
         <v>11</v>
@@ -4383,7 +4380,7 @@
     </row>
     <row r="74" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B74" t="s">
         <v>13</v>
@@ -4430,7 +4427,7 @@
     </row>
     <row r="75" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B75" t="s">
         <v>13</v>
@@ -4477,7 +4474,7 @@
     </row>
     <row r="76" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B76" t="s">
         <v>13</v>
@@ -4524,7 +4521,7 @@
     </row>
     <row r="77" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B77" t="s">
         <v>13</v>
@@ -4563,7 +4560,7 @@
         <v>141</v>
       </c>
       <c r="N77" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="O77" t="s">
         <v>9</v>
